--- a/public/templates/shift-report.xlsx
+++ b/public/templates/shift-report.xlsx
@@ -3606,7 +3606,7 @@
         <v>70</v>
       </c>
       <c r="I5" s="183"/>
-      <c r="J5" s="182"/>
+      <c r="J5" s="183"/>
       <c r="K5" s="183"/>
       <c r="L5" s="183"/>
       <c r="M5" s="183"/>
